--- a/Stats Publication Leads.xlsx
+++ b/Stats Publication Leads.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zna25d\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A011D78F-2570-4BA1-98C6-795D2E1F8044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD16BDAF-592F-4900-B757-07598C4DEAB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-3732" yWindow="-17388" windowWidth="30936" windowHeight="16776" xr2:uid="{D9DAD797-3196-47A8-927E-B65CA5FE599E}"/>
   </bookViews>
@@ -104,12 +104,6 @@
     <t>https://www.gov.uk/government/collections/electronic-monitoring-publication</t>
   </si>
   <si>
-    <t>Helen Fairbanks</t>
-  </si>
-  <si>
-    <t>Saleyah Miah</t>
-  </si>
-  <si>
     <t>Yes</t>
   </si>
   <si>
@@ -556,15 +550,9 @@
     <t>https://www.gov.uk/government/collections/youth-custody-data</t>
   </si>
   <si>
-    <t xml:space="preserve">Katherine Tatlock / Pete Burgess </t>
-  </si>
-  <si>
     <t>Jamie Newton</t>
   </si>
   <si>
-    <t>Katherine Tatlock</t>
-  </si>
-  <si>
     <t>YCSInformationAndPerformance@justice.gov.uk</t>
   </si>
   <si>
@@ -662,6 +650,18 @@
   </si>
   <si>
     <t>MHCSMailbox@justice.gov.uk</t>
+  </si>
+  <si>
+    <t>Anna Hollywood</t>
+  </si>
+  <si>
+    <t>Tara Rose</t>
+  </si>
+  <si>
+    <t>Carly Gray</t>
+  </si>
+  <si>
+    <t>Louisa Hutton-Adams</t>
   </si>
 </sst>
 </file>
@@ -1288,10 +1288,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1696,562 +1692,562 @@
         <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>25</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>27</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>12</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="H4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>32</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>34</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>12</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>40</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>12</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="H6" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="E7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="F7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="D8" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="E8" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="F8" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="H8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="F9" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="G9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="D10" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="F10" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D10" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="G10" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I10" s="1"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="D11" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="E11" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="F11" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="D12" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="E12" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="F12" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="D13" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="F13" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="D14" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="F14" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D14" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="E14" s="1" t="s">
+      <c r="H14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="D15" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="F15" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="D16" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="F16" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="D17" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="E17" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="F17" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="D18" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>110</v>
-      </c>
       <c r="E18" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>55</v>
+        <v>204</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="E19" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D19" s="10" t="s">
+      <c r="F19" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="G19" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="H19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I19" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="D20" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="E20" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="F20" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="G20" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="D21" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="E21" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D21" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="F21" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="D22" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>134</v>
-      </c>
       <c r="E22" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>16</v>
@@ -2260,19 +2256,19 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="D23" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="E23" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>139</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
@@ -2280,405 +2276,405 @@
         <v>16</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="D24" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C24" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="F24" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>148</v>
-      </c>
       <c r="D25" s="10" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C26" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>151</v>
-      </c>
       <c r="D26" s="10" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C27" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="D27" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="E27" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="D27" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>156</v>
-      </c>
       <c r="F27" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="F29" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C29" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="E29" s="1" t="s">
+      <c r="G29" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>165</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>167</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>169</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>12</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>172</v>
+        <v>205</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E32" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="H32" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="I32" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="G33" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="H33" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I33" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D34" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="F34" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H35" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="F36" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="H36" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I36" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -2688,6 +2684,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3d62609a-7e30-44b8-a432-cdf7356e24ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="351d582a-7b6f-46d7-8ce9-09297641bd46" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BFA604A9C3983C42BD25AD6B677D13E2" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0b7b66054bf514abfae6322c23004b28">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3d62609a-7e30-44b8-a432-cdf7356e24ea" xmlns:ns3="351d582a-7b6f-46d7-8ce9-09297641bd46" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="791102654b535ba2954fb47e85e2201c" ns2:_="" ns3:_="">
     <xsd:import namespace="3d62609a-7e30-44b8-a432-cdf7356e24ea"/>
@@ -2916,17 +2923,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3d62609a-7e30-44b8-a432-cdf7356e24ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="351d582a-7b6f-46d7-8ce9-09297641bd46" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2937,6 +2933,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{604A6221-C1B2-41C8-8D4F-4E88F9B37FB1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3d62609a-7e30-44b8-a432-cdf7356e24ea"/>
+    <ds:schemaRef ds:uri="351d582a-7b6f-46d7-8ce9-09297641bd46"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A97A81B0-2DF2-468B-B6AD-3D7D9D3DB556}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2955,17 +2962,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{604A6221-C1B2-41C8-8D4F-4E88F9B37FB1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3d62609a-7e30-44b8-a432-cdf7356e24ea"/>
-    <ds:schemaRef ds:uri="351d582a-7b6f-46d7-8ce9-09297641bd46"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11924491-05F8-4976-B631-407825EBE43A}">
   <ds:schemaRefs>
